--- a/grupos/2BEM - Estadisticos 20232.xlsx
+++ b/grupos/2BEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -179,21 +179,21 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
+    <t>Sanchez Morales Gilberto</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
@@ -218,45 +218,48 @@
     <t>CORDOVA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ECHAVARRIA</t>
+  </si>
+  <si>
     <t>ESCOBEDO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OROZCO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>SAAVEDRA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OROZCO</t>
-  </si>
-  <si>
-    <t>SAAVEDRA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -269,30 +272,33 @@
     <t>MARCELINO</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
     <t>NAIDELYN</t>
   </si>
   <si>
@@ -302,43 +308,46 @@
     <t>ANA KAREN</t>
   </si>
   <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>ELIAS IGNACIO</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
     <t>JOSE EMMANUEL</t>
   </si>
   <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOANNA OCTAVIA</t>
   </si>
   <si>
     <t>IAN</t>
   </si>
   <si>
+    <t>JOSE ARTURO</t>
+  </si>
+  <si>
+    <t>ARELY SUSANA</t>
+  </si>
+  <si>
     <t>YAEL ISSAI</t>
-  </si>
-  <si>
-    <t>ELIAS IGNACIO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOANNA OCTAVIA</t>
-  </si>
-  <si>
-    <t>JOSE ARTURO</t>
-  </si>
-  <si>
-    <t>ARELY SUSANA</t>
   </si>
 </sst>
 </file>
@@ -903,28 +912,28 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -957,28 +966,28 @@
         <v>-1</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE4">
         <v>5</v>
       </c>
       <c r="AF4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>5</v>
       </c>
       <c r="AH4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI4">
         <v>6</v>
       </c>
       <c r="AJ4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK4">
         <v>-1</v>
@@ -1016,28 +1025,28 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1079,19 +1088,19 @@
         <v>7</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG5">
         <v>6</v>
       </c>
       <c r="AH5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI5">
         <v>7</v>
       </c>
       <c r="AJ5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK5">
         <v>-1</v>
@@ -1129,28 +1138,28 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1183,7 +1192,7 @@
         <v>-1</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD6">
         <v>5</v>
@@ -1192,19 +1201,19 @@
         <v>9</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6">
         <v>9</v>
       </c>
       <c r="AH6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI6">
         <v>7</v>
       </c>
       <c r="AJ6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK6">
         <v>-1</v>
@@ -1242,28 +1251,28 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1355,28 +1364,28 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1409,13 +1418,13 @@
         <v>-1</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD8">
         <v>5</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF8">
         <v>7</v>
@@ -1424,13 +1433,13 @@
         <v>6</v>
       </c>
       <c r="AH8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI8">
         <v>6</v>
       </c>
       <c r="AJ8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK8">
         <v>-1</v>
@@ -1468,28 +1477,28 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1525,7 +1534,7 @@
         <v>9</v>
       </c>
       <c r="AD9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE9">
         <v>7</v>
@@ -1581,28 +1590,28 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1635,7 +1644,7 @@
         <v>-1</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AD10">
         <v>5</v>
@@ -1650,13 +1659,13 @@
         <v>6</v>
       </c>
       <c r="AH10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI10">
         <v>6</v>
       </c>
       <c r="AJ10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK10">
         <v>-1</v>
@@ -1694,28 +1703,28 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1751,19 +1760,19 @@
         <v>7</v>
       </c>
       <c r="AD11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE11">
         <v>9</v>
       </c>
       <c r="AF11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG11">
         <v>6</v>
       </c>
       <c r="AH11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI11">
         <v>7</v>
@@ -1807,28 +1816,28 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1861,7 +1870,7 @@
         <v>-1</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AD12">
         <v>10</v>
@@ -1876,7 +1885,7 @@
         <v>8</v>
       </c>
       <c r="AH12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI12">
         <v>10</v>
@@ -1920,28 +1929,28 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1983,13 +1992,13 @@
         <v>9</v>
       </c>
       <c r="AF13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG13">
         <v>9</v>
       </c>
       <c r="AH13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI13">
         <v>8</v>
@@ -2033,28 +2042,28 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -2102,7 +2111,7 @@
         <v>6</v>
       </c>
       <c r="AH14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI14">
         <v>6</v>
@@ -2146,28 +2155,28 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -2218,7 +2227,7 @@
         <v>5</v>
       </c>
       <c r="AI15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ15">
         <v>5</v>
@@ -2259,28 +2268,28 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2313,16 +2322,16 @@
         <v>-1</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE16">
         <v>7</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG16">
         <v>9</v>
@@ -2331,7 +2340,7 @@
         <v>5</v>
       </c>
       <c r="AI16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ16">
         <v>9</v>
@@ -2372,28 +2381,28 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2426,13 +2435,13 @@
         <v>-1</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF17">
         <v>7</v>
@@ -2441,7 +2450,7 @@
         <v>6</v>
       </c>
       <c r="AH17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI17">
         <v>5</v>
@@ -2485,28 +2494,28 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2560,7 +2569,7 @@
         <v>6</v>
       </c>
       <c r="AJ18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK18">
         <v>-1</v>
@@ -2598,28 +2607,28 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2652,10 +2661,10 @@
         <v>-1</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE19">
         <v>9</v>
@@ -2667,10 +2676,10 @@
         <v>9</v>
       </c>
       <c r="AH19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ19">
         <v>8</v>
@@ -2711,28 +2720,28 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2768,25 +2777,25 @@
         <v>9</v>
       </c>
       <c r="AD20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE20">
         <v>9</v>
       </c>
       <c r="AF20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG20">
         <v>9</v>
       </c>
       <c r="AH20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK20">
         <v>-1</v>
@@ -2824,28 +2833,28 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2881,7 +2890,7 @@
         <v>10</v>
       </c>
       <c r="AD21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE21">
         <v>9</v>
@@ -2896,10 +2905,10 @@
         <v>10</v>
       </c>
       <c r="AI21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK21">
         <v>-1</v>
@@ -2937,28 +2946,28 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2991,7 +3000,7 @@
         <v>-1</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD22">
         <v>6</v>
@@ -3006,13 +3015,13 @@
         <v>7</v>
       </c>
       <c r="AH22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI22">
         <v>6</v>
       </c>
       <c r="AJ22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK22">
         <v>-1</v>
@@ -3050,28 +3059,28 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -3104,7 +3113,7 @@
         <v>-1</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD23">
         <v>10</v>
@@ -3119,7 +3128,7 @@
         <v>9</v>
       </c>
       <c r="AH23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI23">
         <v>8</v>
@@ -3163,28 +3172,28 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -3276,28 +3285,28 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -3345,7 +3354,7 @@
         <v>9</v>
       </c>
       <c r="AH25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI25">
         <v>10</v>
@@ -3389,28 +3398,28 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -3446,19 +3455,19 @@
         <v>8</v>
       </c>
       <c r="AD26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE26">
         <v>9</v>
       </c>
       <c r="AF26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG26">
         <v>6</v>
       </c>
       <c r="AH26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI26">
         <v>7</v>
@@ -3502,28 +3511,28 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -3565,7 +3574,7 @@
         <v>5</v>
       </c>
       <c r="AF27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG27">
         <v>5</v>
@@ -3577,7 +3586,7 @@
         <v>5</v>
       </c>
       <c r="AJ27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK27">
         <v>-1</v>
@@ -3761,22 +3770,22 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L4">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O4">
         <v>53.3</v>
       </c>
       <c r="P4">
-        <v>62.5</v>
+        <v>68.8</v>
       </c>
       <c r="Q4">
         <v>85</v>
@@ -3788,22 +3797,22 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U4">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
       <c r="W4">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X4">
         <v>53.3</v>
       </c>
       <c r="Y4">
-        <v>62.5</v>
+        <v>68.8</v>
       </c>
       <c r="Z4">
         <v>85</v>
@@ -3847,16 +3856,16 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L5">
-        <v>94.7</v>
+        <v>95</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -3865,7 +3874,7 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -3874,16 +3883,16 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U5">
-        <v>94.7</v>
+        <v>95</v>
       </c>
       <c r="V5">
         <v>100</v>
       </c>
       <c r="W5">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X5">
         <v>100</v>
@@ -3892,7 +3901,7 @@
         <v>100</v>
       </c>
       <c r="Z5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA5">
         <v>100</v>
@@ -3933,16 +3942,16 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L6">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="M6">
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3960,16 +3969,16 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U6">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="V6">
         <v>100</v>
       </c>
       <c r="W6">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -3995,7 +4004,7 @@
         <v>83.3</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -4019,10 +4028,10 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -4034,10 +4043,10 @@
         <v>93.3</v>
       </c>
       <c r="P7">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4046,10 +4055,10 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -4061,10 +4070,10 @@
         <v>93.3</v>
       </c>
       <c r="Y7">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="Z7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AA7">
         <v>100</v>
@@ -4105,10 +4114,10 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L8">
-        <v>94.7</v>
+        <v>95</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4132,10 +4141,10 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U8">
-        <v>94.7</v>
+        <v>95</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4277,22 +4286,22 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L10">
-        <v>94.7</v>
+        <v>92.5</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4304,22 +4313,22 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U10">
-        <v>94.7</v>
+        <v>92.5</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X10">
         <v>100</v>
       </c>
       <c r="Y10">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z10">
         <v>100</v>
@@ -4363,52 +4372,52 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M11">
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q11">
+        <v>90</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="U11">
         <v>95</v>
       </c>
-      <c r="R11">
-        <v>100</v>
-      </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-      <c r="T11">
-        <v>91.7</v>
-      </c>
-      <c r="U11">
-        <v>100</v>
-      </c>
       <c r="V11">
         <v>100</v>
       </c>
       <c r="W11">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="X11">
         <v>100</v>
       </c>
       <c r="Y11">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z11">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA11">
         <v>100</v>
@@ -4449,7 +4458,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4458,7 +4467,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O12">
         <v>93.3</v>
@@ -4467,7 +4476,7 @@
         <v>93.8</v>
       </c>
       <c r="Q12">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4476,7 +4485,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4485,7 +4494,7 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X12">
         <v>93.3</v>
@@ -4494,7 +4503,7 @@
         <v>93.8</v>
       </c>
       <c r="Z12">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="AA12">
         <v>100</v>
@@ -4535,7 +4544,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -4544,7 +4553,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O13">
         <v>86.7</v>
@@ -4553,7 +4562,7 @@
         <v>93.8</v>
       </c>
       <c r="Q13">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4562,7 +4571,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4571,7 +4580,7 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X13">
         <v>86.7</v>
@@ -4580,7 +4589,7 @@
         <v>93.8</v>
       </c>
       <c r="Z13">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="AA13">
         <v>100</v>
@@ -4621,22 +4630,22 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L14">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O14">
         <v>86.7</v>
       </c>
       <c r="P14">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q14">
         <v>95</v>
@@ -4648,22 +4657,22 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U14">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X14">
         <v>86.7</v>
       </c>
       <c r="Y14">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z14">
         <v>95</v>
@@ -4707,25 +4716,25 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
       <c r="L15">
-        <v>84.2</v>
+        <v>40</v>
       </c>
       <c r="M15">
         <v>100</v>
       </c>
       <c r="N15">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="O15">
         <v>80</v>
       </c>
       <c r="P15">
-        <v>62.5</v>
+        <v>31.3</v>
       </c>
       <c r="Q15">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -4734,25 +4743,25 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
       <c r="U15">
-        <v>84.2</v>
+        <v>40</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="X15">
         <v>80</v>
       </c>
       <c r="Y15">
-        <v>62.5</v>
+        <v>31.3</v>
       </c>
       <c r="Z15">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA15">
         <v>100</v>
@@ -4793,52 +4802,52 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L16">
-        <v>89.5</v>
+        <v>95</v>
       </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O16">
         <v>93.3</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q16">
+        <v>92.5</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="U16">
         <v>95</v>
       </c>
-      <c r="R16">
-        <v>100</v>
-      </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-      <c r="T16">
-        <v>100</v>
-      </c>
-      <c r="U16">
-        <v>89.5</v>
-      </c>
       <c r="V16">
         <v>100</v>
       </c>
       <c r="W16">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X16">
         <v>93.3</v>
       </c>
       <c r="Y16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z16">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="AA16">
         <v>100</v>
@@ -4879,16 +4888,16 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L17">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4897,7 +4906,7 @@
         <v>93.8</v>
       </c>
       <c r="Q17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4906,16 +4915,16 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U17">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="V17">
         <v>100</v>
       </c>
       <c r="W17">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="X17">
         <v>100</v>
@@ -4924,7 +4933,7 @@
         <v>93.8</v>
       </c>
       <c r="Z17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="AA17">
         <v>100</v>
@@ -4965,25 +4974,25 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="L18">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4992,25 +5001,25 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="U18">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="V18">
         <v>100</v>
       </c>
       <c r="W18">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="X18">
         <v>100</v>
       </c>
       <c r="Y18">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z18">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="AA18">
         <v>100</v>
@@ -5051,16 +5060,16 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L19">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -5078,16 +5087,16 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U19">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="V19">
         <v>100</v>
       </c>
       <c r="W19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -5137,16 +5146,16 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L20">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -5164,16 +5173,16 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U20">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="V20">
         <v>100</v>
       </c>
       <c r="W20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X20">
         <v>100</v>
@@ -5223,7 +5232,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5232,16 +5241,16 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5250,7 +5259,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -5259,16 +5268,16 @@
         <v>100</v>
       </c>
       <c r="W21">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="X21">
         <v>100</v>
       </c>
       <c r="Y21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Z21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AA21">
         <v>100</v>
@@ -5309,22 +5318,22 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L22">
-        <v>89.5</v>
+        <v>90</v>
       </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O22">
         <v>86.7</v>
       </c>
       <c r="P22">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q22">
         <v>95</v>
@@ -5336,22 +5345,22 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U22">
-        <v>89.5</v>
+        <v>90</v>
       </c>
       <c r="V22">
         <v>100</v>
       </c>
       <c r="W22">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="X22">
         <v>86.7</v>
       </c>
       <c r="Y22">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z22">
         <v>95</v>
@@ -5395,7 +5404,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -5404,7 +5413,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O23">
         <v>80</v>
@@ -5413,7 +5422,7 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5422,7 +5431,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5431,7 +5440,7 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="X23">
         <v>80</v>
@@ -5440,7 +5449,7 @@
         <v>100</v>
       </c>
       <c r="Z23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA23">
         <v>100</v>
@@ -5481,7 +5490,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>40.9</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -5490,13 +5499,13 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="O24">
         <v>93.3</v>
       </c>
       <c r="P24">
-        <v>81.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q24">
         <v>85</v>
@@ -5508,7 +5517,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>40.9</v>
       </c>
       <c r="U24">
         <v>0</v>
@@ -5517,13 +5526,13 @@
         <v>100</v>
       </c>
       <c r="W24">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="X24">
         <v>93.3</v>
       </c>
       <c r="Y24">
-        <v>81.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Z24">
         <v>85</v>
@@ -5653,52 +5662,52 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L26">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O26">
         <v>80</v>
       </c>
       <c r="P26">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q26">
+        <v>90</v>
+      </c>
+      <c r="R26">
+        <v>100</v>
+      </c>
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="U26">
+        <v>97.5</v>
+      </c>
+      <c r="V26">
+        <v>100</v>
+      </c>
+      <c r="W26">
         <v>95</v>
-      </c>
-      <c r="R26">
-        <v>100</v>
-      </c>
-      <c r="S26">
-        <v>100</v>
-      </c>
-      <c r="T26">
-        <v>91.7</v>
-      </c>
-      <c r="U26">
-        <v>94.7</v>
-      </c>
-      <c r="V26">
-        <v>100</v>
-      </c>
-      <c r="W26">
-        <v>100</v>
       </c>
       <c r="X26">
         <v>80</v>
       </c>
       <c r="Y26">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z26">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA26">
         <v>100</v>
@@ -5739,16 +5748,16 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="L27">
-        <v>84.2</v>
+        <v>85</v>
       </c>
       <c r="M27">
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -5757,7 +5766,7 @@
         <v>81.3</v>
       </c>
       <c r="Q27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5766,16 +5775,16 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="U27">
-        <v>84.2</v>
+        <v>85</v>
       </c>
       <c r="V27">
         <v>100</v>
       </c>
       <c r="W27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X27">
         <v>100</v>
@@ -5784,7 +5793,7 @@
         <v>81.3</v>
       </c>
       <c r="Z27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA27">
         <v>100</v>
@@ -5885,19 +5894,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>45.8</v>
+        <v>58.3</v>
       </c>
       <c r="G3" s="2">
-        <v>54.2</v>
+        <v>41.7</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5908,7 +5917,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -5917,19 +5926,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>54.2</v>
+        <v>75</v>
       </c>
       <c r="G4" s="2">
-        <v>45.8</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5940,7 +5949,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -5949,19 +5958,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>70.8</v>
+        <v>75</v>
       </c>
       <c r="G5" s="2">
-        <v>29.2</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5972,7 +5981,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -5993,7 +6002,7 @@
         <v>25</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6004,7 +6013,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -6013,19 +6022,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>83.3</v>
+        <v>79.2</v>
       </c>
       <c r="G7" s="2">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6036,7 +6045,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -6057,7 +6066,7 @@
         <v>16.7</v>
       </c>
       <c r="H8">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6077,19 +6086,19 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="G9" s="2">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="H9">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6171,7 +6180,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6209,10 +6218,10 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6232,10 +6241,10 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -6255,10 +6264,10 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6278,10 +6287,10 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -6301,10 +6310,10 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6324,10 +6333,10 @@
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -6341,22 +6350,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920034</v>
+        <v>23330051920035</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6364,16 +6373,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920034</v>
+        <v>23330051920035</v>
       </c>
       <c r="B9" t="s">
         <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -6387,22 +6396,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920035</v>
+        <v>23330051920037</v>
       </c>
       <c r="B10" t="s">
         <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6410,16 +6419,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920035</v>
+        <v>23330051920037</v>
       </c>
       <c r="B11" t="s">
         <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -6433,22 +6442,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920037</v>
+        <v>23330051920032</v>
       </c>
       <c r="B12" t="s">
         <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6456,16 +6465,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920037</v>
+        <v>23330051920032</v>
       </c>
       <c r="B13" t="s">
         <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -6479,39 +6488,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920043</v>
+        <v>23330051920031</v>
       </c>
       <c r="B14" t="s">
         <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920043</v>
+        <v>23330051920033</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
@@ -6525,39 +6534,39 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920046</v>
+        <v>23330051920034</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920046</v>
+        <v>23330051920232</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
@@ -6571,16 +6580,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920031</v>
+        <v>23330051920040</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
@@ -6594,16 +6603,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920033</v>
+        <v>23330051920041</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
@@ -6617,16 +6626,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920232</v>
+        <v>23330051920042</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
         <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
         <v>13</v>
@@ -6640,16 +6649,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920040</v>
+        <v>23330051920043</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E21" t="s">
         <v>13</v>
@@ -6663,16 +6672,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920041</v>
+        <v>23330051920044</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
         <v>13</v>
@@ -6686,16 +6695,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920042</v>
+        <v>23330051920209</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
         <v>13</v>
@@ -6709,16 +6718,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920044</v>
+        <v>23330051920046</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s">
         <v>13</v>
@@ -6727,29 +6736,6 @@
         <v>51</v>
       </c>
       <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920209</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2BEM - Estadisticos 20232.xlsx
+++ b/grupos/2BEM - Estadisticos 20232.xlsx
@@ -924,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>7</v>
@@ -936,7 +936,7 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -978,7 +978,7 @@
         <v>7</v>
       </c>
       <c r="AG4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH4">
         <v>6</v>
@@ -1037,7 +1037,7 @@
         <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>5</v>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1091,7 +1091,7 @@
         <v>8</v>
       </c>
       <c r="AG5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH5">
         <v>7</v>
@@ -1150,7 +1150,7 @@
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>5</v>
@@ -1162,7 +1162,7 @@
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1263,7 +1263,7 @@
         <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -1275,7 +1275,7 @@
         <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1317,7 +1317,7 @@
         <v>7</v>
       </c>
       <c r="AG7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH7">
         <v>5</v>
@@ -1376,7 +1376,7 @@
         <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>5</v>
@@ -1388,7 +1388,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1430,7 +1430,7 @@
         <v>7</v>
       </c>
       <c r="AG8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH8">
         <v>7</v>
@@ -1489,7 +1489,7 @@
         <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>8</v>
@@ -1501,7 +1501,7 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1602,7 +1602,7 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>7</v>
@@ -1614,7 +1614,7 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1656,7 +1656,7 @@
         <v>10</v>
       </c>
       <c r="AG10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH10">
         <v>6</v>
@@ -1715,7 +1715,7 @@
         <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>5</v>
@@ -1727,7 +1727,7 @@
         <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1828,7 +1828,7 @@
         <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>10</v>
@@ -1840,7 +1840,7 @@
         <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1882,7 +1882,7 @@
         <v>10</v>
       </c>
       <c r="AG12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH12">
         <v>8</v>
@@ -1941,7 +1941,7 @@
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>9</v>
@@ -1953,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1995,7 +1995,7 @@
         <v>8</v>
       </c>
       <c r="AG13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH13">
         <v>8</v>
@@ -2054,7 +2054,7 @@
         <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>9</v>
@@ -2066,7 +2066,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -2108,7 +2108,7 @@
         <v>8</v>
       </c>
       <c r="AG14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH14">
         <v>8</v>
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>5</v>
@@ -2179,7 +2179,7 @@
         <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -2221,7 +2221,7 @@
         <v>5</v>
       </c>
       <c r="AG15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH15">
         <v>5</v>
@@ -2280,7 +2280,7 @@
         <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -2292,7 +2292,7 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2393,7 +2393,7 @@
         <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>10</v>
@@ -2405,7 +2405,7 @@
         <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2447,7 +2447,7 @@
         <v>7</v>
       </c>
       <c r="AG17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH17">
         <v>8</v>
@@ -2506,7 +2506,7 @@
         <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -2518,7 +2518,7 @@
         <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2560,7 +2560,7 @@
         <v>9</v>
       </c>
       <c r="AG18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH18">
         <v>5</v>
@@ -2619,7 +2619,7 @@
         <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>10</v>
@@ -2631,7 +2631,7 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2732,7 +2732,7 @@
         <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>10</v>
@@ -2744,7 +2744,7 @@
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2845,7 +2845,7 @@
         <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>9</v>
@@ -2857,7 +2857,7 @@
         <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2958,7 +2958,7 @@
         <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>10</v>
@@ -2970,7 +2970,7 @@
         <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -3071,7 +3071,7 @@
         <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>9</v>
@@ -3083,7 +3083,7 @@
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -3125,7 +3125,7 @@
         <v>10</v>
       </c>
       <c r="AG23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH23">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>5</v>
@@ -3196,7 +3196,7 @@
         <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -3297,7 +3297,7 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>10</v>
@@ -3309,7 +3309,7 @@
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -3410,7 +3410,7 @@
         <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -3464,7 +3464,7 @@
         <v>8</v>
       </c>
       <c r="AG26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH26">
         <v>6</v>
@@ -3523,7 +3523,7 @@
         <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>5</v>
@@ -3535,7 +3535,7 @@
         <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3782,7 +3782,7 @@
         <v>96.7</v>
       </c>
       <c r="O4">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
       <c r="P4">
         <v>68.8</v>
@@ -3809,7 +3809,7 @@
         <v>96.7</v>
       </c>
       <c r="X4">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
       <c r="Y4">
         <v>68.8</v>
@@ -3868,7 +3868,7 @@
         <v>93.3</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3895,7 +3895,7 @@
         <v>93.3</v>
       </c>
       <c r="X5">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -4298,7 +4298,7 @@
         <v>96.7</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="P10">
         <v>96.90000000000001</v>
@@ -4325,7 +4325,7 @@
         <v>96.7</v>
       </c>
       <c r="X10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Y10">
         <v>96.90000000000001</v>
@@ -4384,7 +4384,7 @@
         <v>88.3</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="P11">
         <v>90.59999999999999</v>
@@ -4411,7 +4411,7 @@
         <v>88.3</v>
       </c>
       <c r="X11">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="Y11">
         <v>90.59999999999999</v>
@@ -4470,7 +4470,7 @@
         <v>93.3</v>
       </c>
       <c r="O12">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="P12">
         <v>93.8</v>
@@ -4497,7 +4497,7 @@
         <v>93.3</v>
       </c>
       <c r="X12">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="Y12">
         <v>93.8</v>
@@ -4642,7 +4642,7 @@
         <v>96.7</v>
       </c>
       <c r="O14">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="P14">
         <v>90.59999999999999</v>
@@ -4669,7 +4669,7 @@
         <v>96.7</v>
       </c>
       <c r="X14">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="Y14">
         <v>90.59999999999999</v>
@@ -4728,7 +4728,7 @@
         <v>1.7</v>
       </c>
       <c r="O15">
-        <v>80</v>
+        <v>46.7</v>
       </c>
       <c r="P15">
         <v>31.3</v>
@@ -4755,7 +4755,7 @@
         <v>1.7</v>
       </c>
       <c r="X15">
-        <v>80</v>
+        <v>46.7</v>
       </c>
       <c r="Y15">
         <v>31.3</v>
@@ -4814,7 +4814,7 @@
         <v>93.3</v>
       </c>
       <c r="O16">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="P16">
         <v>96.90000000000001</v>
@@ -4841,7 +4841,7 @@
         <v>93.3</v>
       </c>
       <c r="X16">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="Y16">
         <v>96.90000000000001</v>
@@ -4900,7 +4900,7 @@
         <v>98.3</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="P17">
         <v>93.8</v>
@@ -4927,7 +4927,7 @@
         <v>98.3</v>
       </c>
       <c r="X17">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Y17">
         <v>93.8</v>
@@ -4986,7 +4986,7 @@
         <v>91.7</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="P18">
         <v>84.40000000000001</v>
@@ -5013,7 +5013,7 @@
         <v>91.7</v>
       </c>
       <c r="X18">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="Y18">
         <v>84.40000000000001</v>
@@ -5072,7 +5072,7 @@
         <v>98.3</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="P19">
         <v>93.8</v>
@@ -5099,7 +5099,7 @@
         <v>98.3</v>
       </c>
       <c r="X19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Y19">
         <v>93.8</v>
@@ -5158,7 +5158,7 @@
         <v>96.7</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -5185,7 +5185,7 @@
         <v>96.7</v>
       </c>
       <c r="X20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -5330,7 +5330,7 @@
         <v>98.3</v>
       </c>
       <c r="O22">
-        <v>86.7</v>
+        <v>80</v>
       </c>
       <c r="P22">
         <v>96.90000000000001</v>
@@ -5357,7 +5357,7 @@
         <v>98.3</v>
       </c>
       <c r="X22">
-        <v>86.7</v>
+        <v>80</v>
       </c>
       <c r="Y22">
         <v>96.90000000000001</v>
@@ -5416,7 +5416,7 @@
         <v>98.3</v>
       </c>
       <c r="O23">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -5443,7 +5443,7 @@
         <v>98.3</v>
       </c>
       <c r="X23">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="Y23">
         <v>100</v>
@@ -5502,7 +5502,7 @@
         <v>91.7</v>
       </c>
       <c r="O24">
-        <v>93.3</v>
+        <v>83.3</v>
       </c>
       <c r="P24">
         <v>65.59999999999999</v>
@@ -5529,7 +5529,7 @@
         <v>91.7</v>
       </c>
       <c r="X24">
-        <v>93.3</v>
+        <v>83.3</v>
       </c>
       <c r="Y24">
         <v>65.59999999999999</v>
@@ -5760,7 +5760,7 @@
         <v>96.7</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="P27">
         <v>81.3</v>
@@ -5787,7 +5787,7 @@
         <v>96.7</v>
       </c>
       <c r="X27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Y27">
         <v>81.3</v>
@@ -6054,19 +6054,19 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="G8" s="2">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="H8">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/2BEM - Estadisticos 20232.xlsx
+++ b/grupos/2BEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="123">
   <si>
     <t>Materia</t>
   </si>
@@ -176,30 +176,30 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
+    <t>Flores Paz Victor</t>
   </si>
   <si>
     <t>Sanchez Morales Gilberto</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Flores Paz Victor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,12 +212,36 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>CORDOVA</t>
   </si>
   <si>
+    <t>ECHAVARRIA</t>
+  </si>
+  <si>
+    <t>ESCOBEDO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -227,16 +251,7 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
+    <t>MEJIA</t>
   </si>
   <si>
     <t>MENDEZ</t>
@@ -260,30 +275,39 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>PANZO</t>
   </si>
   <si>
@@ -299,13 +323,37 @@
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JAZIEL</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
     <t>NAIDELYN</t>
   </si>
   <si>
+    <t>ELIAS IGNACIO</t>
+  </si>
+  <si>
     <t>JOSE GUADALUPE</t>
   </si>
   <si>
-    <t>ANA KAREN</t>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
   </si>
   <si>
     <t>JOSE LUIS</t>
@@ -317,16 +365,7 @@
     <t>EDUARDO</t>
   </si>
   <si>
-    <t>ELIAS IGNACIO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
+    <t>JOSE FRANCISCO</t>
   </si>
   <si>
     <t>ALAN URIEL</t>
@@ -939,40 +978,40 @@
         <v>5</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD4">
         <v>6</v>
       </c>
       <c r="AE4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF4">
         <v>7</v>
@@ -981,7 +1020,7 @@
         <v>6</v>
       </c>
       <c r="AH4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI4">
         <v>6</v>
@@ -1052,52 +1091,52 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ5">
         <v>9</v>
@@ -1165,46 +1204,46 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>7</v>
       </c>
       <c r="AD6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF6">
         <v>9</v>
       </c>
       <c r="AG6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH6">
         <v>8</v>
@@ -1278,52 +1317,52 @@
         <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>5</v>
       </c>
       <c r="AD7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ7">
         <v>6</v>
@@ -1391,43 +1430,43 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC8">
         <v>7</v>
       </c>
       <c r="AD8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE8">
         <v>8</v>
       </c>
       <c r="AF8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8">
         <v>7</v>
@@ -1504,31 +1543,31 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -1543,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH9">
         <v>9</v>
@@ -1617,49 +1656,49 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>6</v>
       </c>
       <c r="AD10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE10">
         <v>7</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG10">
         <v>7</v>
       </c>
       <c r="AH10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI10">
         <v>6</v>
@@ -1730,40 +1769,40 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF11">
         <v>9</v>
@@ -1772,7 +1811,7 @@
         <v>6</v>
       </c>
       <c r="AH11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI11">
         <v>7</v>
@@ -1843,31 +1882,31 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>6</v>
@@ -1879,10 +1918,10 @@
         <v>9</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH12">
         <v>8</v>
@@ -1956,31 +1995,31 @@
         <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -2069,37 +2108,37 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>7</v>
       </c>
       <c r="AD14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE14">
         <v>9</v>
@@ -2182,31 +2221,31 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -2230,7 +2269,7 @@
         <v>5</v>
       </c>
       <c r="AJ15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK15">
         <v>-1</v>
@@ -2295,34 +2334,34 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD16">
         <v>7</v>
@@ -2337,13 +2376,13 @@
         <v>9</v>
       </c>
       <c r="AH16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK16">
         <v>-1</v>
@@ -2408,34 +2447,34 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD17">
         <v>7</v>
@@ -2453,10 +2492,10 @@
         <v>8</v>
       </c>
       <c r="AI17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK17">
         <v>-1</v>
@@ -2521,49 +2560,49 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG18">
         <v>7</v>
       </c>
       <c r="AH18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI18">
         <v>6</v>
@@ -2634,31 +2673,31 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>7</v>
@@ -2670,7 +2709,7 @@
         <v>9</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG19">
         <v>9</v>
@@ -2679,7 +2718,7 @@
         <v>9</v>
       </c>
       <c r="AI19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ19">
         <v>8</v>
@@ -2747,31 +2786,31 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC20">
         <v>9</v>
@@ -2860,31 +2899,31 @@
         <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>10</v>
@@ -2902,7 +2941,7 @@
         <v>9</v>
       </c>
       <c r="AH21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI21">
         <v>8</v>
@@ -2973,31 +3012,31 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>7</v>
@@ -3009,7 +3048,7 @@
         <v>9</v>
       </c>
       <c r="AF22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG22">
         <v>7</v>
@@ -3086,31 +3125,31 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -3119,13 +3158,13 @@
         <v>10</v>
       </c>
       <c r="AE23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF23">
         <v>10</v>
       </c>
       <c r="AG23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH23">
         <v>9</v>
@@ -3199,40 +3238,40 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC24">
         <v>5</v>
       </c>
       <c r="AD24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF24">
         <v>6</v>
@@ -3244,10 +3283,10 @@
         <v>5</v>
       </c>
       <c r="AI24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK24">
         <v>-1</v>
@@ -3312,31 +3351,31 @@
         <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -3357,10 +3396,10 @@
         <v>9</v>
       </c>
       <c r="AI25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK25">
         <v>-1</v>
@@ -3425,31 +3464,31 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC26">
         <v>8</v>
@@ -3464,10 +3503,10 @@
         <v>8</v>
       </c>
       <c r="AG26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI26">
         <v>7</v>
@@ -3538,52 +3577,52 @@
         <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>5</v>
       </c>
       <c r="AD27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ27">
         <v>6</v>
@@ -3797,25 +3836,25 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U4">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
       <c r="W4">
-        <v>96.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X4">
-        <v>73.3</v>
+        <v>83.3</v>
       </c>
       <c r="Y4">
-        <v>68.8</v>
+        <v>79.2</v>
       </c>
       <c r="Z4">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="AA4">
         <v>100</v>
@@ -3883,25 +3922,25 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>95.5</v>
+        <v>75</v>
       </c>
       <c r="U5">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="V5">
         <v>100</v>
       </c>
       <c r="W5">
-        <v>93.3</v>
+        <v>80.2</v>
       </c>
       <c r="X5">
-        <v>93.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y5">
         <v>100</v>
       </c>
       <c r="Z5">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="AA5">
         <v>100</v>
@@ -3969,16 +4008,16 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V6">
         <v>100</v>
       </c>
       <c r="W6">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -4055,10 +4094,10 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="U7">
-        <v>85</v>
+        <v>90.3</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -4067,13 +4106,13 @@
         <v>100</v>
       </c>
       <c r="X7">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="Y7">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="Z7">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA7">
         <v>100</v>
@@ -4141,22 +4180,22 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U8">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="V8">
         <v>100</v>
       </c>
       <c r="W8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X8">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y8">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z8">
         <v>100</v>
@@ -4313,25 +4352,25 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U10">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X10">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="Y10">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z10">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA10">
         <v>100</v>
@@ -4399,25 +4438,25 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>86.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="U11">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="V11">
         <v>100</v>
       </c>
       <c r="W11">
-        <v>88.3</v>
+        <v>88.5</v>
       </c>
       <c r="X11">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Y11">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z11">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="AA11">
         <v>100</v>
@@ -4485,7 +4524,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4494,16 +4533,16 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>93.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="X12">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Y12">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z12">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="AA12">
         <v>100</v>
@@ -4571,7 +4610,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4580,16 +4619,16 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X13">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="Y13">
-        <v>93.8</v>
+        <v>83.3</v>
       </c>
       <c r="Z13">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="AA13">
         <v>100</v>
@@ -4657,25 +4696,25 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="X14">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="Y14">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z14">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA14">
         <v>100</v>
@@ -4743,31 +4782,31 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>63.6</v>
+        <v>43.8</v>
       </c>
       <c r="U15">
-        <v>40</v>
+        <v>25.8</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="X15">
-        <v>46.7</v>
+        <v>29.2</v>
       </c>
       <c r="Y15">
-        <v>31.3</v>
+        <v>20.8</v>
       </c>
       <c r="Z15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AA15">
         <v>100</v>
       </c>
       <c r="AB15">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -4829,25 +4868,25 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U16">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="V16">
         <v>100</v>
       </c>
       <c r="W16">
-        <v>93.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X16">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="Y16">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z16">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="AA16">
         <v>100</v>
@@ -4915,25 +4954,25 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U17">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V17">
         <v>100</v>
       </c>
       <c r="W17">
-        <v>98.3</v>
+        <v>91.7</v>
       </c>
       <c r="X17">
-        <v>96.7</v>
+        <v>93.8</v>
       </c>
       <c r="Y17">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z17">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA17">
         <v>100</v>
@@ -5001,25 +5040,25 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>72.7</v>
+        <v>81.3</v>
       </c>
       <c r="U18">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
       </c>
       <c r="W18">
-        <v>91.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X18">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="Y18">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Z18">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="AA18">
         <v>100</v>
@@ -5087,22 +5126,22 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V19">
         <v>100</v>
       </c>
       <c r="W19">
-        <v>98.3</v>
+        <v>93.8</v>
       </c>
       <c r="X19">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y19">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z19">
         <v>100</v>
@@ -5173,19 +5212,19 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U20">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V20">
         <v>100</v>
       </c>
       <c r="W20">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X20">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -5259,7 +5298,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -5268,16 +5307,16 @@
         <v>100</v>
       </c>
       <c r="W21">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="X21">
         <v>100</v>
       </c>
       <c r="Y21">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z21">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA21">
         <v>100</v>
@@ -5345,25 +5384,25 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U22">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="V22">
         <v>100</v>
       </c>
       <c r="W22">
-        <v>98.3</v>
+        <v>91.7</v>
       </c>
       <c r="X22">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Y22">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z22">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="AA22">
         <v>100</v>
@@ -5431,7 +5470,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5440,16 +5479,16 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>98.3</v>
+        <v>95.8</v>
       </c>
       <c r="X23">
-        <v>86.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Y23">
         <v>100</v>
       </c>
       <c r="Z23">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="AA23">
         <v>100</v>
@@ -5466,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -5493,7 +5532,7 @@
         <v>40.9</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -5517,25 +5556,25 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>40.9</v>
+        <v>59.4</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24">
         <v>100</v>
       </c>
       <c r="W24">
-        <v>91.7</v>
+        <v>86.5</v>
       </c>
       <c r="X24">
-        <v>83.3</v>
+        <v>70.8</v>
       </c>
       <c r="Y24">
-        <v>65.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Z24">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="AA24">
         <v>100</v>
@@ -5689,25 +5728,25 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V26">
         <v>100</v>
       </c>
       <c r="W26">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="X26">
-        <v>80</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Y26">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Z26">
-        <v>90</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AA26">
         <v>100</v>
@@ -5775,25 +5814,25 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>77.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U27">
-        <v>85</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="V27">
         <v>100</v>
       </c>
       <c r="W27">
-        <v>96.7</v>
+        <v>93.8</v>
       </c>
       <c r="X27">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y27">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Z27">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="AA27">
         <v>100</v>
@@ -5885,7 +5924,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -5894,16 +5933,16 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>58.3</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2">
-        <v>41.7</v>
+        <v>25</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -5917,7 +5956,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -5926,16 +5965,16 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="G4" s="2">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
         <v>7.5</v>
@@ -5949,7 +5988,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -5958,19 +5997,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>75</v>
+        <v>91.7</v>
       </c>
       <c r="G5" s="2">
-        <v>25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5981,7 +6020,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -5990,19 +6029,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>75</v>
+        <v>95.8</v>
       </c>
       <c r="G6" s="2">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6013,7 +6052,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -6022,19 +6061,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>79.2</v>
+        <v>95.8</v>
       </c>
       <c r="G7" s="2">
-        <v>20.8</v>
+        <v>4.2</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6045,7 +6084,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -6054,19 +6093,19 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>87.5</v>
+        <v>95.8</v>
       </c>
       <c r="G8" s="2">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="H8">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6077,7 +6116,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>58</v>
@@ -6086,19 +6125,19 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>87.5</v>
+        <v>95.8</v>
       </c>
       <c r="G9" s="2">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="H9">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6109,7 +6148,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -6118,19 +6157,19 @@
         <v>24</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G10" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -6180,7 +6219,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6212,19 +6251,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920029</v>
+        <v>23330051920181</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>52</v>
@@ -6235,16 +6274,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920029</v>
+        <v>23330051920181</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -6258,22 +6297,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920030</v>
+        <v>23330051920028</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6281,16 +6320,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920030</v>
+        <v>23330051920028</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -6307,16 +6346,16 @@
         <v>22330051920007</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>52</v>
@@ -6330,13 +6369,13 @@
         <v>22330051920007</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -6350,19 +6389,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920035</v>
+        <v>23330051920039</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>52</v>
@@ -6373,16 +6412,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920035</v>
+        <v>23330051920039</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -6396,22 +6435,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920037</v>
+        <v>23330051920212</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6419,16 +6458,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920037</v>
+        <v>23330051920212</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -6442,39 +6481,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920032</v>
+        <v>23330051920029</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920032</v>
+        <v>23330051920031</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -6488,16 +6527,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920031</v>
+        <v>23330051920030</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
@@ -6514,13 +6553,13 @@
         <v>23330051920033</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
@@ -6537,13 +6576,13 @@
         <v>23330051920034</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
@@ -6560,13 +6599,13 @@
         <v>23330051920232</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
@@ -6580,16 +6619,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920040</v>
+        <v>23330051920035</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
@@ -6603,16 +6642,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920041</v>
+        <v>23330051920037</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
@@ -6626,16 +6665,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920042</v>
+        <v>23330051920032</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E20" t="s">
         <v>13</v>
@@ -6649,16 +6688,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920043</v>
+        <v>22330051920021</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E21" t="s">
         <v>13</v>
@@ -6672,16 +6711,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920044</v>
+        <v>23330051920040</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
         <v>13</v>
@@ -6695,16 +6734,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920209</v>
+        <v>23330051920041</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E23" t="s">
         <v>13</v>
@@ -6718,16 +6757,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920046</v>
+        <v>23330051920042</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E24" t="s">
         <v>13</v>
@@ -6736,6 +6775,98 @@
         <v>51</v>
       </c>
       <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920043</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>23330051920044</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920209</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920046</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2BEM - Estadisticos 20232.xlsx
+++ b/grupos/2BEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -173,30 +173,30 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Flores Paz Victor</t>
+  </si>
+  <si>
+    <t>Sanchez Morales Gilberto</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Flores Paz Victor</t>
-  </si>
-  <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
@@ -212,12 +212,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -227,60 +227,12 @@
     <t>VERA</t>
   </si>
   <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OROZCO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SAAVEDRA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>DAMIAN</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -290,45 +242,12 @@
     <t>VILLA</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
+    <t>IRVING</t>
   </si>
   <si>
     <t>JESUS JAREF</t>
   </si>
   <si>
-    <t>IRVING</t>
-  </si>
-  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
@@ -336,57 +255,6 @@
   </si>
   <si>
     <t>ALEX URIEL</t>
-  </si>
-  <si>
-    <t>NAIDELYN</t>
-  </si>
-  <si>
-    <t>ELIAS IGNACIO</t>
-  </si>
-  <si>
-    <t>JOSE GUADALUPE</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOANNA OCTAVIA</t>
-  </si>
-  <si>
-    <t>IAN</t>
-  </si>
-  <si>
-    <t>JOSE ARTURO</t>
-  </si>
-  <si>
-    <t>ARELY SUSANA</t>
-  </si>
-  <si>
-    <t>YAEL ISSAI</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +897,7 @@
         <v>6</v>
       </c>
       <c r="AK4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1142,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="AK5">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1255,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="AK6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1368,7 +1236,7 @@
         <v>6</v>
       </c>
       <c r="AK7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1481,7 +1349,7 @@
         <v>8</v>
       </c>
       <c r="AK8">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1594,7 +1462,7 @@
         <v>9</v>
       </c>
       <c r="AK9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1707,7 +1575,7 @@
         <v>8</v>
       </c>
       <c r="AK10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1820,7 +1688,7 @@
         <v>8</v>
       </c>
       <c r="AK11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1933,7 +1801,7 @@
         <v>9</v>
       </c>
       <c r="AK12">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2046,7 +1914,7 @@
         <v>8</v>
       </c>
       <c r="AK13">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2159,7 +2027,7 @@
         <v>7</v>
       </c>
       <c r="AK14">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2272,7 +2140,7 @@
         <v>6</v>
       </c>
       <c r="AK15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2385,7 +2253,7 @@
         <v>8</v>
       </c>
       <c r="AK16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2498,7 +2366,7 @@
         <v>6</v>
       </c>
       <c r="AK17">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2611,7 +2479,7 @@
         <v>7</v>
       </c>
       <c r="AK18">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2724,7 +2592,7 @@
         <v>8</v>
       </c>
       <c r="AK19">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2837,7 +2705,7 @@
         <v>9</v>
       </c>
       <c r="AK20">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2950,7 +2818,7 @@
         <v>9</v>
       </c>
       <c r="AK21">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3063,7 +2931,7 @@
         <v>8</v>
       </c>
       <c r="AK22">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3176,7 +3044,7 @@
         <v>9</v>
       </c>
       <c r="AK23">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3289,7 +3157,7 @@
         <v>6</v>
       </c>
       <c r="AK24">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3402,7 +3270,7 @@
         <v>9</v>
       </c>
       <c r="AK25">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3515,7 +3383,7 @@
         <v>8</v>
       </c>
       <c r="AK26">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -3628,7 +3496,7 @@
         <v>6</v>
       </c>
       <c r="AK27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5895,7 +5763,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
@@ -5904,27 +5772,30 @@
         <v>24</v>
       </c>
       <c r="D2">
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>75</v>
+      </c>
+      <c r="G2" s="2">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>24</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -5933,19 +5804,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="G3" s="2">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5956,7 +5827,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -5965,19 +5836,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="G4" s="2">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5988,7 +5859,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -5997,19 +5868,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="G5" s="2">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6020,7 +5891,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -6041,7 +5912,7 @@
         <v>4.2</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6052,7 +5923,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -6073,7 +5944,7 @@
         <v>4.2</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6084,7 +5955,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -6105,7 +5976,7 @@
         <v>4.2</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6116,7 +5987,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>58</v>
@@ -6137,7 +6008,7 @@
         <v>4.2</v>
       </c>
       <c r="H9">
-        <v>6.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6219,7 +6090,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6251,19 +6122,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920181</v>
+        <v>23330051920028</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>52</v>
@@ -6274,45 +6145,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920181</v>
+        <v>23330051920028</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920028</v>
+        <v>23330051920181</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6320,45 +6191,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920028</v>
+        <v>22330051920007</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>51</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920007</v>
+        <v>23330051920039</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6366,508 +6237,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920007</v>
+        <v>23330051920212</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>51</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920039</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920039</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920212</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920212</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920029</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920031</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920030</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920033</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920034</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920232</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920035</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920037</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920032</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920021</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920040</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" t="s">
-        <v>116</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920041</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" t="s">
-        <v>117</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920042</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920043</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" t="s">
-        <v>119</v>
-      </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920044</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920209</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>121</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920046</v>
-      </c>
-      <c r="B28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" t="s">
-        <v>122</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
